--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test3/ACCOUNTS_RECEIVABLE.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test3/ACCOUNTS_RECEIVABLE.xlsx
@@ -11,6 +11,31 @@
     <sheet name="Query" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0">
+      <text>
+        <t>Run the initialization SQL once.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0">
+      <text>
+        <t>Execute the SQL statement for the starting values\n once to select rows from the table.</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0">
+      <text>
+        <t>Run the finalize SQL once.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53,7 +78,22 @@
     </comment>
     <comment ref="B1" authorId="0">
       <text>
-        <t>Execute SQL with column names in AS and set to the group name of the column sheet, the results of the SELECT SQL will be used sequentially.</t>
+        <t>Execute SQL with column names in AS and set to the group name of the column sheet.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>offset for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <t>NEXT_VALUE OR RANDOM</t>
       </text>
     </comment>
   </commentList>
@@ -61,28 +101,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Table Name</t>
   </si>
   <si>
-    <t>[1] Setup SQL
-(1 execution)</t>
-  </si>
-  <si>
-    <t>[2] Start Value SQL
-(1 execution)</t>
-  </si>
-  <si>
-    <t>[3] Number of Rows</t>
+    <t>[1] Setup SQL</t>
+  </si>
+  <si>
+    <t>[2] Start Value SQL</t>
+  </si>
+  <si>
+    <t>[3] Row amplification factor</t>
   </si>
   <si>
     <t>[4] Insert SQL
-([2]×[3] execution)</t>
-  </si>
-  <si>
-    <t>[5] Finalize SQL
-(1 execution)</t>
+([2]×[3] rows insert.)</t>
+  </si>
+  <si>
+    <t>[5] Finalize SQL</t>
   </si>
   <si>
     <t>ACCOUNTS_RECEIVABLE</t>
@@ -92,11 +129,18 @@
   </si>
   <si>
     <t>SELECT
-	a.CUSTOMER_ID AS CUSTOMER_ID
-FROM CUSTOMERS a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSERT INTO ACCOUNTS_RECEIVABLE 
+	a.CUSTOMER_ID
+FROM CUSTOMERS a
+WHERE NOT EXISTS
+(
+	SELECT 1
+	FROM ACCOUNTS_RECEIVABLE b
+	WHERE
+	b.CUSTOMER_ID = a.CUSTOMER_ID
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT INTO ACCOUNTS_RECEIVABLE
 (
 	  CUSTOMER_ID
 	, BALANCE_AMOUNT
@@ -174,6 +218,15 @@
     <t>Select SQL</t>
   </si>
   <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Selection Strategy</t>
+  </si>
+  <si>
     <t>Group1</t>
   </si>
   <si>
@@ -182,6 +235,9 @@
 	, 0 AS BALANCE_AMOUNT
 	, '1970-01-01 09:00:00' AS UPDATED_AT
 FROM (VALUES(0))</t>
+  </si>
+  <si>
+    <t>NEXT_VALUE</t>
   </si>
 </sst>
 </file>
@@ -189,13 +245,61 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="329">
+  <fonts count="341">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1568,7 +1672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
@@ -1607,25 +1711,25 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
@@ -2051,15 +2155,33 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="322" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="324" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -2074,8 +2196,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -2134,6 +2260,8 @@
     <row r="7"/>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2356,11 +2484,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.25390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.390625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2370,13 +2501,31 @@
       <c r="B1" s="162" t="s">
         <v>30</v>
       </c>
+      <c r="C1" s="163" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="164" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="165" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2" ht="75.0" customHeight="true">
-      <c r="A2" s="163" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="164" t="s">
-        <v>32</v>
+      <c r="A2" s="166" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="167" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="168" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="169" t="n">
+        <v>2.147483647E9</v>
+      </c>
+      <c r="E2" s="170" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test3/ACCOUNTS_RECEIVABLE.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test3/ACCOUNTS_RECEIVABLE.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Table" r:id="rId3" sheetId="1"/>
     <sheet name="Column" r:id="rId4" sheetId="2"/>
     <sheet name="Query" r:id="rId5" sheetId="3"/>
+    <sheet name="File" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -83,17 +84,72 @@
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <t>offset for SELECT SQL.</t>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
-        <t>limit for SELECT SQL.</t>
+        <t>offset for SELECT SQL.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
         <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>If the name given here is set to the group name of the column sheet, the results of the SELECT SQL will be used.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that reads data sources such as files and returns an iterable of Map objects.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>offset for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
       </text>
     </comment>
   </commentList>
@@ -101,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Table Name</t>
   </si>
@@ -218,6 +274,9 @@
     <t>Select SQL</t>
   </si>
   <si>
+    <t>Column Mapping Expression</t>
+  </si>
+  <si>
     <t>Offset</t>
   </si>
   <si>
@@ -225,6 +284,9 @@
   </si>
   <si>
     <t>Selection Strategy</t>
+  </si>
+  <si>
+    <t>Selection Strategy weight expression</t>
   </si>
   <si>
     <t>Group1</t>
@@ -238,6 +300,25 @@
   </si>
   <si>
     <t>NEXT_VALUE</t>
+  </si>
+  <si>
+    <t>DataSource Expression</t>
+  </si>
+  <si>
+    <t>FileGroup1</t>
+  </si>
+  <si>
+    <t>[
+	["a":"1", "b":2]
+	,["a":"3", "b":4]
+]</t>
+  </si>
+  <si>
+    <t>[
+"col_a":a
+,"col_b":b
+,"col_c":"cccc"
+]</t>
   </si>
 </sst>
 </file>
@@ -245,13 +326,157 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="341">
+  <fonts count="377">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1672,7 +1897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
@@ -2169,11 +2394,11 @@
     <xf numFmtId="0" fontId="330" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="332" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="332" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="336" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
@@ -2182,6 +2407,60 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="340" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -2197,6 +2476,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -2484,14 +2767,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="5.85546875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2510,23 +2795,96 @@
       <c r="E1" s="165" t="s">
         <v>33</v>
       </c>
+      <c r="F1" s="166" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="167" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" ht="75.0" customHeight="true">
-      <c r="A2" s="166" t="s">
+      <c r="A2" s="168" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="169" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="171" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="172" t="n">
+        <v>2.147483647E9</v>
+      </c>
+      <c r="F2" s="173" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="174"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="175" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="177" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="178" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="179" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="167" t="s">
+      <c r="G1" s="181" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="168" t="n">
+    </row>
+    <row r="2" ht="75.0" customHeight="true">
+      <c r="A2" s="182" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="183" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="184" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="185" t="n">
         <v>0.0</v>
       </c>
-      <c r="D2" s="169" t="n">
+      <c r="E2" s="186" t="n">
         <v>2.147483647E9</v>
       </c>
-      <c r="E2" s="170" t="s">
-        <v>36</v>
-      </c>
+      <c r="F2" s="187" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="188"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
